--- a/PC_2019/03-KarimnagarPC_SircillaAS_Form_20.xlsx
+++ b/PC_2019/03-KarimnagarPC_SircillaAS_Form_20.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,19 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +70,32 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +117,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +176,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,11 +560,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V136"/>
+  <dimension ref="A1:W138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -520,107 +615,112 @@
           <t>PS_No</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PS_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>PONNAM PRABHAKER</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>BANDI SANJAY KUMAR</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>BOIANAPALLI VINOD KUMAR</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>KANNA ANAGANDULA</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>ANILKUMAR CHINTHA</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>AILA PRASANNA</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>EPALLE PRASHANTH</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>REDDY VENUGOPAL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>KOTA SHYAMKUMAR</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>SINGARAPU THIRUPATHI</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>CHILIVERU SRIKANTH</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>SRINIVASA REDDY PAKALA</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>GABBA BHANU LAXMAN</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>BUKKISA RATHNAKAR REDDY</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>RAMESHBABU SHANIGARAPU</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Total_Valid_Votes</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Rejected_Votes</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>NOTA</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Checksum_Diff</t>
         </is>
@@ -630,8 +730,10 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Vanpalli</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>0</v>
@@ -640,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -679,11 +781,11 @@
         <v>0</v>
       </c>
       <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" s="4" t="n">
         <v>0</v>
       </c>
@@ -691,15 +793,21 @@
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <f>SUM(C6:Q6)-R6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Garjanapalli</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>0</v>
@@ -747,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0</v>
@@ -760,14 +868,20 @@
       </c>
       <c r="V7" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <f>SUM(C7:Q7)-R7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Garjanapalli</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>0</v>
@@ -776,11 +890,11 @@
         <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
@@ -815,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>0</v>
@@ -827,15 +941,21 @@
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <f>SUM(C8:Q8)-R8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Adavipadira</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>0</v>
@@ -877,11 +997,11 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>540</v>
       </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
@@ -895,30 +1015,36 @@
         <v>0</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>540</v>
+        <v>0</v>
+      </c>
+      <c r="W9" s="4">
+        <f>SUM(C9:Q9)-R9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Kancharla</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
@@ -936,20 +1062,20 @@
         <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>474</v>
       </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
@@ -963,19 +1089,25 @@
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>901</v>
+        <v>0</v>
+      </c>
+      <c r="W10" s="4">
+        <f>SUM(C10:Q10)-R10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Racharla Boppapur</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D11" s="4" t="n">
         <v>0</v>
       </c>
@@ -1004,20 +1136,20 @@
         <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
         <v>358</v>
       </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>359</v>
       </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
@@ -1031,15 +1163,21 @@
         <v>0</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>719</v>
+        <v>0</v>
+      </c>
+      <c r="W11" s="4">
+        <f>SUM(C11:Q11)-R11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Racharla Boppapur</t>
+        </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>0</v>
@@ -1069,11 +1207,11 @@
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
@@ -1099,15 +1237,21 @@
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="W12" s="4">
+        <f>SUM(C12:Q12)-R12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>0</v>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Thimmapur</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>0</v>
@@ -1119,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
@@ -1167,15 +1311,21 @@
         <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W13" s="4">
+        <f>SUM(C13:Q13)-R13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Gundaram</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>0</v>
@@ -1193,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>0</v>
@@ -1235,25 +1385,31 @@
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W14" s="4">
+        <f>SUM(C14:Q14)-R14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Gajasingavaram</t>
+        </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
@@ -1276,11 +1432,11 @@
         <v>0</v>
       </c>
       <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
         <v>462</v>
       </c>
-      <c r="N15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" s="4" t="n">
         <v>0</v>
       </c>
@@ -1303,21 +1459,27 @@
         <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>468</v>
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <f>SUM(C15:Q15)-R15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Gajasingavaram</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
@@ -1350,14 +1512,14 @@
         <v>0</v>
       </c>
       <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>205</v>
       </c>
-      <c r="Q16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
@@ -1371,21 +1533,27 @@
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>209</v>
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <f>SUM(C16:Q16)-R16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Narmala</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>1</v>
@@ -1394,23 +1562,23 @@
         <v>1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K17" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" s="4" t="n">
         <v>0</v>
       </c>
@@ -1439,15 +1607,21 @@
         <v>0</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="W17" s="4">
+        <f>SUM(C17:Q17)-R17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Gambiraopet</t>
+        </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>0</v>
@@ -1459,41 +1633,41 @@
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="K18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="L18" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>703</v>
       </c>
-      <c r="Q18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
@@ -1507,18 +1681,24 @@
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1443</v>
+        <v>0</v>
+      </c>
+      <c r="W18" s="4">
+        <f>SUM(C18:Q18)-R18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>1</v>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -1533,35 +1713,35 @@
         <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="J19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="L19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>440</v>
       </c>
-      <c r="N19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="Q19" s="4" t="n">
         <v>442</v>
       </c>
-      <c r="Q19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" s="4" t="n">
         <v>0</v>
       </c>
@@ -1575,27 +1755,33 @@
         <v>0</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>903</v>
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <f>SUM(C19:Q19)-R19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>0</v>
@@ -1604,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0</v>
@@ -1625,14 +1811,14 @@
         <v>0</v>
       </c>
       <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" s="4" t="n">
         <v>0</v>
       </c>
@@ -1643,15 +1829,21 @@
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="W20" s="4">
+        <f>SUM(C20:Q20)-R20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>0</v>
@@ -1693,11 +1885,11 @@
         <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>258</v>
       </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" s="4" t="n">
         <v>0</v>
       </c>
@@ -1711,24 +1903,30 @@
         <v>0</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>258</v>
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
+        <f>SUM(C21:Q21)-R21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>1</v>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
@@ -1752,20 +1950,20 @@
         <v>0</v>
       </c>
       <c r="M22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n">
         <v>481</v>
       </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="Q22" s="4" t="n">
         <v>483</v>
       </c>
-      <c r="Q22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" s="4" t="n">
         <v>0</v>
       </c>
@@ -1779,21 +1977,27 @@
         <v>0</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>971</v>
+        <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <f>SUM(C22:Q22)-R22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>0</v>
@@ -1808,26 +2012,26 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="n">
         <v>605</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="O23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
       </c>
@@ -1847,15 +2051,21 @@
         <v>0</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>645</v>
+        <v>0</v>
+      </c>
+      <c r="W23" s="4">
+        <f>SUM(C23:Q23)-R23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Cheerlavancha</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
@@ -1873,11 +2083,11 @@
         <v>0</v>
       </c>
       <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="4" t="n">
         <v>0</v>
       </c>
@@ -1888,11 +2098,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="n">
         <v>392</v>
       </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" s="4" t="n">
         <v>0</v>
       </c>
@@ -1915,15 +2125,21 @@
         <v>0</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>394</v>
+        <v>0</v>
+      </c>
+      <c r="W24" s="4">
+        <f>SUM(C24:Q24)-R24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>0</v>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Cheerlavancha</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>0</v>
@@ -1984,29 +2200,35 @@
       </c>
       <c r="V25" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="W25" s="4">
+        <f>SUM(C25:Q25)-R25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Cheerlavancha</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>0</v>
@@ -2015,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>2</v>
@@ -2024,20 +2246,20 @@
         <v>2</v>
       </c>
       <c r="M26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="4" t="n">
         <v>419</v>
       </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" s="4" t="n">
         <v>0</v>
       </c>
@@ -2051,15 +2273,21 @@
         <v>0</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>431</v>
+        <v>0</v>
+      </c>
+      <c r="W26" s="4">
+        <f>SUM(C26:Q26)-R26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>0</v>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Chinthaltana</t>
+        </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
@@ -2077,11 +2305,11 @@
         <v>0</v>
       </c>
       <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" s="4" t="n">
         <v>0</v>
       </c>
@@ -2101,11 +2329,11 @@
         <v>0</v>
       </c>
       <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" s="4" t="n">
         <v>0</v>
       </c>
@@ -2119,15 +2347,21 @@
         <v>0</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="W27" s="4">
+        <f>SUM(C27:Q27)-R27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Tadur</t>
+        </is>
       </c>
       <c r="C28" s="4" t="n">
         <v>0</v>
@@ -2148,32 +2382,32 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="n">
         <v>2</v>
       </c>
       <c r="M28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="4" t="n">
         <v>315</v>
       </c>
-      <c r="N28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>318</v>
       </c>
-      <c r="Q28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" s="4" t="n">
         <v>0</v>
       </c>
@@ -2187,61 +2421,67 @@
         <v>0</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>641</v>
+        <v>0</v>
+      </c>
+      <c r="W28" s="4">
+        <f>SUM(C28:Q28)-R28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>1</v>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Gopalraopalli</t>
+        </is>
       </c>
       <c r="C29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="K29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="L29" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>509</v>
       </c>
-      <c r="N29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" s="4" t="n">
         <v>0</v>
       </c>
@@ -2255,18 +2495,24 @@
         <v>0</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>544</v>
+        <v>0</v>
+      </c>
+      <c r="W29" s="4">
+        <f>SUM(C29:Q29)-R29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>1</v>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Laxmipur</t>
+        </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>0</v>
@@ -2281,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>0</v>
@@ -2323,15 +2569,21 @@
         <v>0</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="W30" s="4">
+        <f>SUM(C30:Q30)-R30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>0</v>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Thangalapalli</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>0</v>
@@ -2352,32 +2604,32 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>432</v>
       </c>
-      <c r="N31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4" t="n">
         <v>435</v>
       </c>
-      <c r="Q31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" s="4" t="n">
         <v>0</v>
       </c>
@@ -2391,15 +2643,21 @@
         <v>0</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1077</v>
+        <v>0</v>
+      </c>
+      <c r="W31" s="4">
+        <f>SUM(C31:Q31)-R31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>0</v>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Kasbekatoor</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
         <v>0</v>
@@ -2411,40 +2669,40 @@
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="n">
         <v>440</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="4" t="n">
         <v>0</v>
@@ -2459,43 +2717,49 @@
         <v>0</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>458</v>
+        <v>0</v>
+      </c>
+      <c r="W32" s="4">
+        <f>SUM(C32:Q32)-R32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>0</v>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Pothgal</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="K33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" s="4" t="n">
         <v>0</v>
       </c>
@@ -2506,11 +2770,11 @@
         <v>0</v>
       </c>
       <c r="O33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q33" s="4" t="n">
         <v>0</v>
       </c>
@@ -2527,21 +2791,27 @@
         <v>0</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="W33" s="4">
+        <f>SUM(C33:Q33)-R33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="B34" s="4" t="n">
-        <v>0</v>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Pothgal</t>
+        </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>0</v>
@@ -2556,20 +2826,20 @@
         <v>0</v>
       </c>
       <c r="I34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M34" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" s="4" t="n">
         <v>0</v>
       </c>
@@ -2595,22 +2865,28 @@
         <v>0</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="W34" s="4">
+        <f>SUM(C34:Q34)-R34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
         <v>163</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>0</v>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Avunoor</t>
+        </is>
       </c>
       <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="D35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
@@ -2624,32 +2900,32 @@
         <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="K35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="L35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="N35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4" t="n">
         <v>193</v>
       </c>
-      <c r="Q35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" s="4" t="n">
         <v>0</v>
       </c>
@@ -2663,15 +2939,21 @@
         <v>0</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>422</v>
+        <v>0</v>
+      </c>
+      <c r="W35" s="4">
+        <f>SUM(C35:Q35)-R35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
         <v>164</v>
       </c>
-      <c r="B36" s="4" t="n">
-        <v>0</v>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Thurkapalli</t>
+        </is>
       </c>
       <c r="C36" s="4" t="n">
         <v>0</v>
@@ -2695,29 +2977,29 @@
         <v>0</v>
       </c>
       <c r="J36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="4" t="n">
         <v>587</v>
       </c>
-      <c r="N36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4" t="n">
         <v>504</v>
       </c>
-      <c r="Q36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" s="4" t="n">
         <v>0</v>
       </c>
@@ -2731,61 +3013,67 @@
         <v>0</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>1093</v>
+        <v>0</v>
+      </c>
+      <c r="W36" s="4">
+        <f>SUM(C36:Q36)-R36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Kondapur</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>456</v>
       </c>
-      <c r="N37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>458</v>
       </c>
-      <c r="Q37" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" s="4" t="n">
         <v>0</v>
       </c>
@@ -2799,15 +3087,21 @@
         <v>0</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>933</v>
+        <v>0</v>
+      </c>
+      <c r="W37" s="4">
+        <f>SUM(C37:Q37)-R37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="B38" s="4" t="n">
-        <v>0</v>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Kondapur</t>
+        </is>
       </c>
       <c r="C38" s="4" t="n">
         <v>0</v>
@@ -2840,20 +3134,20 @@
         <v>0</v>
       </c>
       <c r="M38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="n">
         <v>436</v>
       </c>
-      <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4" t="n">
         <v>436</v>
       </c>
-      <c r="Q38" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" s="4" t="n">
         <v>0</v>
       </c>
@@ -2867,21 +3161,27 @@
         <v>0</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>872</v>
+        <v>0</v>
+      </c>
+      <c r="W38" s="4">
+        <f>SUM(C38:Q38)-R38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
         <v>169</v>
       </c>
-      <c r="B39" s="4" t="n">
-        <v>0</v>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Bandalingampalli</t>
+        </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
@@ -2896,11 +3196,11 @@
         <v>0</v>
       </c>
       <c r="I39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
       </c>
@@ -2908,20 +3208,20 @@
         <v>0</v>
       </c>
       <c r="M39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="n">
         <v>419</v>
       </c>
-      <c r="N39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="n">
         <v>425</v>
       </c>
-      <c r="Q39" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" s="4" t="n">
         <v>0</v>
       </c>
@@ -2935,15 +3235,21 @@
         <v>0</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>847</v>
+        <v>0</v>
+      </c>
+      <c r="W39" s="4">
+        <f>SUM(C39:Q39)-R39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
         <v>170</v>
       </c>
-      <c r="B40" s="4" t="n">
-        <v>0</v>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Bandalingampalli</t>
+        </is>
       </c>
       <c r="C40" s="4" t="n">
         <v>0</v>
@@ -2955,20 +3261,20 @@
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
@@ -2976,20 +3282,20 @@
         <v>0</v>
       </c>
       <c r="M40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="4" t="n">
         <v>378</v>
       </c>
-      <c r="N40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4" t="n">
         <v>379</v>
       </c>
-      <c r="Q40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" s="4" t="n">
         <v>0</v>
       </c>
@@ -3003,34 +3309,40 @@
         <v>0</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>765</v>
+        <v>0</v>
+      </c>
+      <c r="W40" s="4">
+        <f>SUM(C40:Q40)-R40</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="B41" s="4" t="n">
-        <v>0</v>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Bandalingampalli</t>
+        </is>
       </c>
       <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
@@ -3038,11 +3350,11 @@
         <v>0</v>
       </c>
       <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" s="4" t="n">
         <v>0</v>
       </c>
@@ -3053,11 +3365,11 @@
         <v>0</v>
       </c>
       <c r="P41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" s="4" t="n">
         <v>0</v>
       </c>
@@ -3071,19 +3383,25 @@
         <v>0</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="W41" s="4">
+        <f>SUM(C41:Q41)-R41</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Lingannapet</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D42" s="4" t="n">
         <v>0</v>
       </c>
@@ -3097,35 +3415,35 @@
         <v>0</v>
       </c>
       <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="K42" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="L42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="n">
         <v>635</v>
       </c>
-      <c r="N42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="4" t="n">
         <v>637</v>
       </c>
-      <c r="Q42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" s="4" t="n">
         <v>0</v>
       </c>
@@ -3139,15 +3457,21 @@
         <v>0</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>1293</v>
+        <v>0</v>
+      </c>
+      <c r="W42" s="4">
+        <f>SUM(C42:Q42)-R42</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="B43" s="4" t="n">
-        <v>0</v>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Lingannapet</t>
+        </is>
       </c>
       <c r="C43" s="4" t="n">
         <v>0</v>
@@ -3159,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>1</v>
@@ -3168,26 +3492,26 @@
         <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O43" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
       </c>
@@ -3195,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="4" t="n">
         <v>0</v>
@@ -3207,27 +3531,33 @@
         <v>0</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="W43" s="4">
+        <f>SUM(C43:Q43)-R43</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
         <v>179</v>
       </c>
-      <c r="B44" s="4" t="n">
-        <v>0</v>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Kothapalli</t>
+        </is>
       </c>
       <c r="C44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="E44" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>0</v>
@@ -3239,29 +3569,29 @@
         <v>0</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="4" t="n">
         <v>418</v>
       </c>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="Q44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" s="4" t="n">
         <v>0</v>
       </c>
@@ -3275,61 +3605,67 @@
         <v>0</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>874</v>
+        <v>0</v>
+      </c>
+      <c r="W44" s="4">
+        <f>SUM(C44:Q44)-R44</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
         <v>187</v>
       </c>
-      <c r="B45" s="4" t="n">
-        <v>0</v>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Mucherla</t>
+        </is>
       </c>
       <c r="C45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="K45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="4" t="n">
+      <c r="L45" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M45" s="4" t="n">
+      <c r="N45" s="4" t="n">
         <v>444</v>
       </c>
-      <c r="N45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="Q45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" s="4" t="n">
         <v>0</v>
       </c>
@@ -3343,15 +3679,21 @@
         <v>0</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>521</v>
+        <v>0</v>
+      </c>
+      <c r="W45" s="4">
+        <f>SUM(C45:Q45)-R45</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="B46" s="4" t="n">
-        <v>0</v>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Chippalapalli</t>
+        </is>
       </c>
       <c r="C46" s="4" t="n">
         <v>0</v>
@@ -3393,14 +3735,14 @@
         <v>0</v>
       </c>
       <c r="P46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4" t="n">
         <v>714</v>
       </c>
-      <c r="Q46" s="4" t="n">
+      <c r="R46" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" s="4" t="n">
         <v>0</v>
       </c>
@@ -3411,22 +3753,28 @@
         <v>0</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>710</v>
+        <v>0</v>
+      </c>
+      <c r="W46" s="4">
+        <f>SUM(C46:Q46)-R46</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
         <v>189</v>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>0</v>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Namapur</t>
+        </is>
       </c>
       <c r="C47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D47" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E47" s="4" t="n">
         <v>0</v>
       </c>
@@ -3479,27 +3827,33 @@
         <v>0</v>
       </c>
       <c r="V47" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="W47" s="4">
+        <f>SUM(C47:Q47)-R47</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Namapur</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="D48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>0</v>
@@ -3520,17 +3874,17 @@
         <v>0</v>
       </c>
       <c r="M48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P48" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q48" s="4" t="n">
         <v>0</v>
       </c>
@@ -3547,15 +3901,21 @@
         <v>0</v>
       </c>
       <c r="V48" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="W48" s="4">
+        <f>SUM(C48:Q48)-R48</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
         <v>193</v>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>0</v>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Chikodu</t>
+        </is>
       </c>
       <c r="C49" s="4" t="n">
         <v>0</v>
@@ -3594,11 +3954,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P49" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q49" s="4" t="n">
         <v>0</v>
       </c>
@@ -3615,39 +3975,45 @@
         <v>0</v>
       </c>
       <c r="V49" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="W49" s="4">
+        <f>SUM(C49:Q49)-R49</f>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="B50" s="4" t="n">
-        <v>1</v>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Mustabad</t>
+        </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I50" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="J50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>0</v>
@@ -3683,15 +4049,21 @@
         <v>0</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="W50" s="4">
+        <f>SUM(C50:Q50)-R50</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="B51" s="4" t="n">
-        <v>0</v>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Mustabad</t>
+        </is>
       </c>
       <c r="C51" s="4" t="n">
         <v>0</v>
@@ -3700,11 +4072,11 @@
         <v>0</v>
       </c>
       <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G51" s="4" t="n">
         <v>0</v>
       </c>
@@ -3727,11 +4099,11 @@
         <v>0</v>
       </c>
       <c r="N51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="O51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P51" s="4" t="n">
         <v>0</v>
       </c>
@@ -3751,52 +4123,58 @@
         <v>0</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="W51" s="4">
+        <f>SUM(C51:Q51)-R51</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="B52" s="4" t="n">
-        <v>1</v>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Morrapur</t>
+        </is>
       </c>
       <c r="C52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E52" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="J52" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="N52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O52" s="4" t="n">
         <v>0</v>
       </c>
@@ -3819,27 +4197,33 @@
         <v>0</v>
       </c>
       <c r="V52" s="4" t="n">
-        <v>61</v>
+        <v>0</v>
+      </c>
+      <c r="W52" s="4">
+        <f>SUM(C52:Q52)-R52</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="B53" s="4" t="n">
-        <v>1</v>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Terlumaddi</t>
+        </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>0</v>
@@ -3851,17 +4235,17 @@
         <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N53" s="4" t="n">
         <v>0</v>
       </c>
@@ -3869,11 +4253,11 @@
         <v>0</v>
       </c>
       <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="Q53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" s="4" t="n">
         <v>0</v>
       </c>
@@ -3887,15 +4271,22 @@
         <v>0</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>112</v>
+        <v>0</v>
+      </c>
+      <c r="W53" s="4">
+        <f>SUM(C53:Q53)-R53</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="B54" s="4" t="n">
-        <v>0</v>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Battuvanithallu
+H/o Terlumaddi</t>
+        </is>
       </c>
       <c r="C54" s="4" t="n">
         <v>0</v>
@@ -3956,17 +4347,23 @@
       </c>
       <c r="V54" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="W54" s="4">
+        <f>SUM(C54:Q54)-R54</f>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
         <v>209</v>
       </c>
-      <c r="B55" s="4" t="n">
-        <v>1</v>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Terlumaddi</t>
+        </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>0</v>
@@ -3975,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>1</v>
@@ -3984,32 +4381,32 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="N55" s="4" t="n">
         <v>413</v>
       </c>
-      <c r="N55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P55" s="4" t="n">
+      <c r="Q55" s="4" t="n">
         <v>417</v>
       </c>
-      <c r="Q55" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" s="4" t="n">
         <v>0</v>
       </c>
@@ -4023,37 +4420,43 @@
         <v>0</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>850</v>
+        <v>0</v>
+      </c>
+      <c r="W55" s="4">
+        <f>SUM(C55:Q55)-R55</f>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="B56" s="4" t="n">
-        <v>1</v>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Jillella</t>
+        </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I56" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" s="4" t="n">
         <v>0</v>
       </c>
@@ -4091,19 +4494,25 @@
         <v>0</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="W56" s="4">
+        <f>SUM(C56:Q56)-R56</f>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
         <v>212</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Jillella</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D57" s="4" t="n">
         <v>0</v>
       </c>
@@ -4111,11 +4520,11 @@
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H57" s="4" t="n">
         <v>0</v>
       </c>
@@ -4126,17 +4535,17 @@
         <v>0</v>
       </c>
       <c r="K57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="n">
         <v>479</v>
       </c>
-      <c r="N57" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O57" s="4" t="n">
         <v>0</v>
       </c>
@@ -4159,24 +4568,30 @@
         <v>0</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>486</v>
+        <v>0</v>
+      </c>
+      <c r="W57" s="4">
+        <f>SUM(C57:Q57)-R57</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="B58" s="4" t="n">
-        <v>0</v>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Desaipalli</t>
+        </is>
       </c>
       <c r="C58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>0</v>
@@ -4185,35 +4600,35 @@
         <v>0</v>
       </c>
       <c r="H58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J58" s="4" t="n">
+      <c r="K58" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>8</v>
       </c>
       <c r="L58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="M58" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N58" s="4" t="n">
         <v>406</v>
       </c>
-      <c r="N58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="Q58" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="Q58" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" s="4" t="n">
         <v>0</v>
       </c>
@@ -4227,15 +4642,21 @@
         <v>0</v>
       </c>
       <c r="V58" s="4" t="n">
-        <v>851</v>
+        <v>0</v>
+      </c>
+      <c r="W58" s="4">
+        <f>SUM(C58:Q58)-R58</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>0</v>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Baddenapalli</t>
+        </is>
       </c>
       <c r="C59" s="4" t="n">
         <v>0</v>
@@ -4244,32 +4665,32 @@
         <v>0</v>
       </c>
       <c r="E59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M59" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="N59" s="4" t="n">
         <v>0</v>
       </c>
@@ -4295,61 +4716,67 @@
         <v>0</v>
       </c>
       <c r="V59" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="W59" s="4">
+        <f>SUM(C59:Q59)-R59</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="B60" s="4" t="n">
-        <v>1</v>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Baswapur</t>
+        </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="M60" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M60" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>418</v>
       </c>
-      <c r="N60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="n">
         <v>425</v>
       </c>
-      <c r="Q60" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" s="4" t="n">
         <v>0</v>
       </c>
@@ -4363,61 +4790,67 @@
         <v>0</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>860</v>
+        <v>0</v>
+      </c>
+      <c r="W60" s="4">
+        <f>SUM(C60:Q60)-R60</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="B61" s="4" t="n">
-        <v>0</v>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Baswapur</t>
+        </is>
       </c>
       <c r="C61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="J61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="n">
         <v>520</v>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="O61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="n">
         <v>525</v>
       </c>
-      <c r="Q61" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" s="4" t="n">
         <v>0</v>
       </c>
@@ -4431,46 +4864,52 @@
         <v>0</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>1067</v>
+        <v>0</v>
+      </c>
+      <c r="W61" s="4">
+        <f>SUM(C61:Q61)-R61</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
         <v>219</v>
       </c>
-      <c r="B62" s="4" t="n">
-        <v>1</v>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Nerella</t>
+        </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J62" s="4" t="n">
+      <c r="K62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K62" s="4" t="n">
+      <c r="L62" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L62" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" s="4" t="n">
         <v>0</v>
       </c>
@@ -4499,15 +4938,21 @@
         <v>0</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="W62" s="4">
+        <f>SUM(C62:Q62)-R62</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
         <v>220</v>
       </c>
-      <c r="B63" s="4" t="n">
-        <v>0</v>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Nerella</t>
+        </is>
       </c>
       <c r="C63" s="4" t="n">
         <v>0</v>
@@ -4549,14 +4994,14 @@
         <v>0</v>
       </c>
       <c r="P63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="Q63" s="4" t="n">
+      <c r="R63" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R63" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S63" s="4" t="n">
         <v>0</v>
       </c>
@@ -4567,15 +5012,21 @@
         <v>0</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="W63" s="4">
+        <f>SUM(C63:Q63)-R63</f>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
         <v>221</v>
       </c>
-      <c r="B64" s="4" t="n">
-        <v>0</v>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Chinnalingapur</t>
+        </is>
       </c>
       <c r="C64" s="4" t="n">
         <v>0</v>
@@ -4620,11 +5071,11 @@
         <v>0</v>
       </c>
       <c r="Q64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="R64" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" s="4" t="n">
         <v>0</v>
       </c>
@@ -4635,61 +5086,67 @@
         <v>0</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
+      </c>
+      <c r="W64" s="4">
+        <f>SUM(C64:Q64)-R64</f>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
         <v>224</v>
       </c>
-      <c r="B65" s="4" t="n">
-        <v>1</v>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 224</t>
+        </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="J65" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J65" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="M65" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M65" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>397</v>
       </c>
-      <c r="N65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="Q65" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" s="4" t="n">
         <v>0</v>
       </c>
@@ -4703,21 +5160,27 @@
         <v>0</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>619</v>
+        <v>0</v>
+      </c>
+      <c r="W65" s="4">
+        <f>SUM(C65:Q65)-R65</f>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
         <v>225</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 225</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
@@ -4744,20 +5207,20 @@
         <v>0</v>
       </c>
       <c r="M66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="4" t="n">
         <v>329</v>
       </c>
-      <c r="N66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="4" t="n">
         <v>381</v>
       </c>
-      <c r="Q66" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" s="4" t="n">
         <v>0</v>
       </c>
@@ -4771,27 +5234,33 @@
         <v>0</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>713</v>
+        <v>0</v>
+      </c>
+      <c r="W66" s="4">
+        <f>SUM(C66:Q66)-R66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
         <v>227</v>
       </c>
-      <c r="B67" s="4" t="n">
-        <v>1</v>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 227</t>
+        </is>
       </c>
       <c r="C67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="4" t="n">
         <v>0</v>
@@ -4800,32 +5269,32 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="K67" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="4" t="n">
+      <c r="L67" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L67" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4" t="n">
         <v>693</v>
       </c>
-      <c r="N67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P67" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>695</v>
       </c>
-      <c r="Q67" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" s="4" t="n">
         <v>0</v>
       </c>
@@ -4839,33 +5308,39 @@
         <v>0</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>1409</v>
+        <v>0</v>
+      </c>
+      <c r="W67" s="4">
+        <f>SUM(C67:Q67)-R67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="B68" s="4" t="n">
-        <v>0</v>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 228</t>
+        </is>
       </c>
       <c r="C68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
@@ -4907,15 +5382,21 @@
         <v>0</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="W68" s="4">
+        <f>SUM(C68:Q68)-R68</f>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
         <v>229</v>
       </c>
-      <c r="B69" s="4" t="n">
-        <v>1</v>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 229</t>
+        </is>
       </c>
       <c r="C69" s="4" t="n">
         <v>1</v>
@@ -4924,43 +5405,43 @@
         <v>1</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="K69" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K69" s="4" t="n">
+      <c r="L69" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L69" s="4" t="n">
+      <c r="M69" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M69" s="4" t="n">
+      <c r="N69" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="N69" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O69" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>5</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R69" s="4" t="n">
         <v>0</v>
@@ -4975,61 +5456,67 @@
         <v>0</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>597</v>
+        <v>0</v>
+      </c>
+      <c r="W69" s="4">
+        <f>SUM(C69:Q69)-R69</f>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 231</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D70" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="I70" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I70" s="4" t="n">
+      <c r="J70" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>5</v>
       </c>
       <c r="L70" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M70" s="4" t="n">
+      <c r="N70" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="N70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="P70" s="4" t="n">
+      <c r="Q70" s="4" t="n">
         <v>799</v>
       </c>
-      <c r="Q70" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" s="4" t="n">
         <v>0</v>
       </c>
@@ -5043,15 +5530,21 @@
         <v>0</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>1562</v>
+        <v>0</v>
+      </c>
+      <c r="W70" s="4">
+        <f>SUM(C70:Q70)-R70</f>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
         <v>233</v>
       </c>
-      <c r="B71" s="4" t="n">
-        <v>0</v>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 233</t>
+        </is>
       </c>
       <c r="C71" s="4" t="n">
         <v>0</v>
@@ -5075,29 +5568,29 @@
         <v>0</v>
       </c>
       <c r="J71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M71" s="4" t="n">
+      <c r="N71" s="4" t="n">
         <v>712</v>
       </c>
-      <c r="N71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Q71" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" s="4" t="n">
         <v>0</v>
       </c>
@@ -5111,15 +5604,21 @@
         <v>0</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>725</v>
+        <v>0</v>
+      </c>
+      <c r="W71" s="4">
+        <f>SUM(C71:Q71)-R71</f>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
         <v>234</v>
       </c>
-      <c r="B72" s="4" t="n">
-        <v>0</v>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 234</t>
+        </is>
       </c>
       <c r="C72" s="4" t="n">
         <v>0</v>
@@ -5134,23 +5633,23 @@
         <v>0</v>
       </c>
       <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="I72" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I72" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L72" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" s="4" t="n">
         <v>0</v>
       </c>
@@ -5179,27 +5678,33 @@
         <v>0</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="W72" s="4">
+        <f>SUM(C72:Q72)-R72</f>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
         <v>237</v>
       </c>
-      <c r="B73" s="4" t="n">
-        <v>1</v>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 237</t>
+        </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>0</v>
@@ -5247,18 +5752,24 @@
         <v>0</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="W73" s="4">
+        <f>SUM(C73:Q73)-R73</f>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="B74" s="4" t="n">
-        <v>1</v>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 238</t>
+        </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" s="4" t="n">
         <v>0</v>
@@ -5273,11 +5784,11 @@
         <v>0</v>
       </c>
       <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I74" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" s="4" t="n">
         <v>0</v>
       </c>
@@ -5291,20 +5802,20 @@
         <v>0</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O74" s="4" t="n">
         <v>4</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R74" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" s="4" t="n">
         <v>0</v>
       </c>
@@ -5315,40 +5826,46 @@
         <v>0</v>
       </c>
       <c r="V74" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="W74" s="4">
+        <f>SUM(C74:Q74)-R74</f>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="B75" s="4" t="n">
-        <v>0</v>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 241</t>
+        </is>
       </c>
       <c r="C75" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E75" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G75" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H75" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J75" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K75" s="4" t="n">
         <v>0</v>
       </c>
@@ -5356,20 +5873,20 @@
         <v>0</v>
       </c>
       <c r="M75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="4" t="n">
         <v>654</v>
       </c>
-      <c r="N75" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O75" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="4" t="n">
         <v>658</v>
       </c>
-      <c r="Q75" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" s="4" t="n">
         <v>0</v>
       </c>
@@ -5383,15 +5900,21 @@
         <v>0</v>
       </c>
       <c r="V75" s="4" t="n">
-        <v>1353</v>
+        <v>0</v>
+      </c>
+      <c r="W75" s="4">
+        <f>SUM(C75:Q75)-R75</f>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="B76" s="4" t="n">
-        <v>0</v>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 242</t>
+        </is>
       </c>
       <c r="C76" s="4" t="n">
         <v>0</v>
@@ -5403,41 +5926,41 @@
         <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J76" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="n">
         <v>604</v>
       </c>
-      <c r="N76" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O76" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="4" t="n">
         <v>611</v>
       </c>
-      <c r="Q76" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" s="4" t="n">
         <v>0</v>
       </c>
@@ -5451,15 +5974,21 @@
         <v>0</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>1220</v>
+        <v>0</v>
+      </c>
+      <c r="W76" s="4">
+        <f>SUM(C76:Q76)-R76</f>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>0</v>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 247</t>
+        </is>
       </c>
       <c r="C77" s="4" t="n">
         <v>0</v>
@@ -5480,11 +6009,11 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J77" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K77" s="4" t="n">
         <v>0</v>
       </c>
@@ -5501,11 +6030,11 @@
         <v>0</v>
       </c>
       <c r="P77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="4" t="n">
         <v>473</v>
       </c>
-      <c r="Q77" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" s="4" t="n">
         <v>0</v>
       </c>
@@ -5519,21 +6048,27 @@
         <v>0</v>
       </c>
       <c r="V77" s="4" t="n">
-        <v>478</v>
+        <v>0</v>
+      </c>
+      <c r="W77" s="4">
+        <f>SUM(C77:Q77)-R77</f>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 248</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>1</v>
@@ -5545,35 +6080,35 @@
         <v>1</v>
       </c>
       <c r="H78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I78" s="4" t="n">
+      <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J78" s="4" t="n">
+      <c r="K78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M78" s="4" t="n">
+      <c r="N78" s="4" t="n">
         <v>553</v>
       </c>
-      <c r="N78" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="O78" s="4" t="n">
         <v>1</v>
       </c>
       <c r="P78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="4" t="n">
         <v>557</v>
       </c>
-      <c r="Q78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" s="4" t="n">
         <v>0</v>
       </c>
@@ -5587,61 +6122,67 @@
         <v>0</v>
       </c>
       <c r="V78" s="4" t="n">
-        <v>1134</v>
+        <v>0</v>
+      </c>
+      <c r="W78" s="4">
+        <f>SUM(C78:Q78)-R78</f>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 252</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C79" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="J79" s="4" t="n">
         <v>18</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="K79" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L79" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M79" s="4" t="n">
+      <c r="N79" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="N79" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P79" s="4" t="n">
+      <c r="Q79" s="4" t="n">
         <v>625</v>
       </c>
-      <c r="Q79" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" s="4" t="n">
         <v>0</v>
       </c>
@@ -5655,18 +6196,24 @@
         <v>0</v>
       </c>
       <c r="V79" s="4" t="n">
-        <v>1282</v>
+        <v>0</v>
+      </c>
+      <c r="W79" s="4">
+        <f>SUM(C79:Q79)-R79</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
         <v>255</v>
       </c>
-      <c r="B80" s="4" t="n">
-        <v>1</v>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 255</t>
+        </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" s="4" t="n">
         <v>0</v>
@@ -5684,11 +6231,11 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J80" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K80" s="4" t="n">
         <v>0</v>
       </c>
@@ -5696,20 +6243,20 @@
         <v>0</v>
       </c>
       <c r="M80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="4" t="n">
         <v>748</v>
       </c>
-      <c r="N80" s="4" t="n">
+      <c r="O80" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O80" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="Q80" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" s="4" t="n">
         <v>0</v>
       </c>
@@ -5723,15 +6270,21 @@
         <v>0</v>
       </c>
       <c r="V80" s="4" t="n">
-        <v>828</v>
+        <v>0</v>
+      </c>
+      <c r="W80" s="4">
+        <f>SUM(C80:Q80)-R80</f>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
         <v>256</v>
       </c>
-      <c r="B81" s="4" t="n">
-        <v>0</v>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 256</t>
+        </is>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -5740,11 +6293,11 @@
         <v>0</v>
       </c>
       <c r="E81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F81" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G81" s="4" t="n">
         <v>0</v>
       </c>
@@ -5752,17 +6305,17 @@
         <v>0</v>
       </c>
       <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J81" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L81" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M81" s="4" t="n">
         <v>0</v>
       </c>
@@ -5791,61 +6344,67 @@
         <v>0</v>
       </c>
       <c r="V81" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="W81" s="4">
+        <f>SUM(C81:Q81)-R81</f>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
         <v>257</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 257</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="D82" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="E82" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="4" t="n">
+      <c r="J82" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J82" s="4" t="n">
+      <c r="K82" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K82" s="4" t="n">
+      <c r="L82" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L82" s="4" t="n">
+      <c r="M82" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M82" s="4" t="n">
+      <c r="N82" s="4" t="n">
         <v>676</v>
       </c>
-      <c r="N82" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P82" s="4" t="n">
+      <c r="Q82" s="4" t="n">
         <v>681</v>
       </c>
-      <c r="Q82" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" s="4" t="n">
         <v>0</v>
       </c>
@@ -5859,61 +6418,67 @@
         <v>0</v>
       </c>
       <c r="V82" s="4" t="n">
-        <v>1404</v>
+        <v>0</v>
+      </c>
+      <c r="W82" s="4">
+        <f>SUM(C82:Q82)-R82</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
         <v>259</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 259</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="C83" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D83" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F83" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H83" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L83" s="4" t="n">
+      <c r="M83" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M83" s="4" t="n">
+      <c r="N83" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="N83" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="P83" s="4" t="n">
+      <c r="Q83" s="4" t="n">
         <v>913</v>
       </c>
-      <c r="Q83" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" s="4" t="n">
         <v>0</v>
       </c>
@@ -5927,61 +6492,67 @@
         <v>0</v>
       </c>
       <c r="V83" s="4" t="n">
-        <v>1931</v>
+        <v>0</v>
+      </c>
+      <c r="W83" s="4">
+        <f>SUM(C83:Q83)-R83</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
         <v>260</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 260</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C84" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D84" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J84" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L84" s="4" t="n">
+      <c r="M84" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M84" s="4" t="n">
+      <c r="N84" s="4" t="n">
         <v>653</v>
       </c>
-      <c r="N84" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="P84" s="4" t="n">
+      <c r="Q84" s="4" t="n">
         <v>662</v>
       </c>
-      <c r="Q84" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" s="4" t="n">
         <v>0</v>
       </c>
@@ -5995,40 +6566,46 @@
         <v>0</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>1345</v>
+        <v>0</v>
+      </c>
+      <c r="W84" s="4">
+        <f>SUM(C84:Q84)-R84</f>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
         <v>264</v>
       </c>
-      <c r="B85" s="4" t="n">
-        <v>0</v>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 264</t>
+        </is>
       </c>
       <c r="C85" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G85" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J85" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
       </c>
@@ -6063,22 +6640,28 @@
         <v>0</v>
       </c>
       <c r="V85" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="W85" s="4">
+        <f>SUM(C85:Q85)-R85</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
         <v>267</v>
       </c>
-      <c r="B86" s="4" t="n">
-        <v>0</v>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 267</t>
+        </is>
       </c>
       <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E86" s="4" t="n">
         <v>0</v>
       </c>
@@ -6089,35 +6672,35 @@
         <v>0</v>
       </c>
       <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I86" s="4" t="n">
+      <c r="J86" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L86" s="4" t="n">
+      <c r="M86" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M86" s="4" t="n">
+      <c r="N86" s="4" t="n">
         <v>543</v>
       </c>
-      <c r="N86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O86" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="4" t="n">
         <v>545</v>
       </c>
-      <c r="Q86" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" s="4" t="n">
         <v>0</v>
       </c>
@@ -6131,61 +6714,67 @@
         <v>0</v>
       </c>
       <c r="V86" s="4" t="n">
-        <v>1106</v>
+        <v>0</v>
+      </c>
+      <c r="W86" s="4">
+        <f>SUM(C86:Q86)-R86</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
         <v>268</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 268</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C87" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="J87" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="K87" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K87" s="4" t="n">
+      <c r="L87" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L87" s="4" t="n">
+      <c r="M87" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M87" s="4" t="n">
+      <c r="N87" s="4" t="n">
         <v>514</v>
       </c>
-      <c r="N87" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P87" s="4" t="n">
+      <c r="Q87" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="Q87" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" s="4" t="n">
         <v>0</v>
       </c>
@@ -6199,37 +6788,43 @@
         <v>0</v>
       </c>
       <c r="V87" s="4" t="n">
-        <v>607</v>
+        <v>0</v>
+      </c>
+      <c r="W87" s="4">
+        <f>SUM(C87:Q87)-R87</f>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
         <v>271</v>
       </c>
-      <c r="B88" s="4" t="n">
-        <v>0</v>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 271</t>
+        </is>
       </c>
       <c r="C88" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G88" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I88" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J88" s="4" t="n">
         <v>0</v>
       </c>
@@ -6240,20 +6835,20 @@
         <v>0</v>
       </c>
       <c r="M88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="4" t="n">
         <v>460</v>
       </c>
-      <c r="N88" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O88" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Q88" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" s="4" t="n">
         <v>0</v>
       </c>
@@ -6267,37 +6862,43 @@
         <v>0</v>
       </c>
       <c r="V88" s="4" t="n">
-        <v>472</v>
+        <v>0</v>
+      </c>
+      <c r="W88" s="4">
+        <f>SUM(C88:Q88)-R88</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
         <v>274</v>
       </c>
-      <c r="B89" s="4" t="n">
-        <v>0</v>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 274</t>
+        </is>
       </c>
       <c r="C89" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F89" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I89" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J89" s="4" t="n">
         <v>0</v>
       </c>
@@ -6308,20 +6909,20 @@
         <v>0</v>
       </c>
       <c r="M89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="4" t="n">
         <v>706</v>
       </c>
-      <c r="N89" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O89" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="4" t="n">
         <v>803</v>
       </c>
-      <c r="Q89" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" s="4" t="n">
         <v>0</v>
       </c>
@@ -6335,15 +6936,21 @@
         <v>0</v>
       </c>
       <c r="V89" s="4" t="n">
-        <v>1519</v>
+        <v>0</v>
+      </c>
+      <c r="W89" s="4">
+        <f>SUM(C89:Q89)-R89</f>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
         <v>278</v>
       </c>
-      <c r="B90" s="4" t="n">
-        <v>0</v>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 278</t>
+        </is>
       </c>
       <c r="C90" s="4" t="n">
         <v>0</v>
@@ -6352,11 +6959,11 @@
         <v>0</v>
       </c>
       <c r="E90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F90" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G90" s="4" t="n">
         <v>0</v>
       </c>
@@ -6388,11 +6995,11 @@
         <v>0</v>
       </c>
       <c r="Q90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R90" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" s="4" t="n">
         <v>0</v>
       </c>
@@ -6403,61 +7010,67 @@
         <v>0</v>
       </c>
       <c r="V90" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="W90" s="4">
+        <f>SUM(C90:Q90)-R90</f>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
         <v>281</v>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 281</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="D91" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="E91" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="F91" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="G91" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="H91" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H91" s="4" t="n">
+      <c r="I91" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I91" s="4" t="n">
+      <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="K91" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="M91" s="4" t="n">
+      <c r="N91" s="4" t="n">
         <v>767</v>
       </c>
-      <c r="N91" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="P91" s="4" t="n">
+      <c r="Q91" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="Q91" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" s="4" t="n">
         <v>0</v>
       </c>
@@ -6471,22 +7084,28 @@
         <v>0</v>
       </c>
       <c r="V91" s="4" t="n">
-        <v>896</v>
+        <v>0</v>
+      </c>
+      <c r="W91" s="4">
+        <f>SUM(C91:Q91)-R91</f>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
         <v>282</v>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 282</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="D92" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D92" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E92" s="4" t="n">
         <v>0</v>
       </c>
@@ -6494,38 +7113,38 @@
         <v>0</v>
       </c>
       <c r="G92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H92" s="4" t="n">
+      <c r="I92" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I92" s="4" t="n">
+      <c r="J92" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J92" s="4" t="n">
+      <c r="K92" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K92" s="4" t="n">
+      <c r="L92" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L92" s="4" t="n">
+      <c r="M92" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M92" s="4" t="n">
+      <c r="N92" s="4" t="n">
         <v>774</v>
       </c>
-      <c r="N92" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="P92" s="4" t="n">
+      <c r="Q92" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="Q92" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" s="4" t="n">
         <v>0</v>
       </c>
@@ -6539,15 +7158,21 @@
         <v>0</v>
       </c>
       <c r="V92" s="4" t="n">
-        <v>893</v>
+        <v>0</v>
+      </c>
+      <c r="W92" s="4">
+        <f>SUM(C92:Q92)-R92</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
         <v>287</v>
       </c>
-      <c r="B93" s="4" t="n">
-        <v>0</v>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 287</t>
+        </is>
       </c>
       <c r="C93" s="4" t="n">
         <v>0</v>
@@ -6583,17 +7208,17 @@
         <v>0</v>
       </c>
       <c r="N93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O93" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q93" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" s="4" t="n">
         <v>0</v>
       </c>
@@ -6607,61 +7232,67 @@
         <v>0</v>
       </c>
       <c r="V93" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="W93" s="4">
+        <f>SUM(C93:Q93)-R93</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
         <v>288</v>
       </c>
-      <c r="B94" s="4" t="n">
-        <v>8</v>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 288</t>
+        </is>
       </c>
       <c r="C94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L94" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" s="4" t="n">
         <v>697</v>
       </c>
-      <c r="N94" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="P94" s="4" t="n">
+      <c r="Q94" s="4" t="n">
         <v>703</v>
       </c>
-      <c r="Q94" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" s="4" t="n">
         <v>0</v>
       </c>
@@ -6675,15 +7306,21 @@
         <v>0</v>
       </c>
       <c r="V94" s="4" t="n">
-        <v>1428</v>
+        <v>0</v>
+      </c>
+      <c r="W94" s="4">
+        <f>SUM(C94:Q94)-R94</f>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="B95" s="4" t="n">
-        <v>0</v>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 289</t>
+        </is>
       </c>
       <c r="C95" s="4" t="n">
         <v>0</v>
@@ -6725,14 +7362,14 @@
         <v>0</v>
       </c>
       <c r="P95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="Q95" s="4" t="n">
+      <c r="R95" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R95" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S95" s="4" t="n">
         <v>0</v>
       </c>
@@ -6743,27 +7380,33 @@
         <v>0</v>
       </c>
       <c r="V95" s="4" t="n">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="W95" s="4">
+        <f>SUM(C95:Q95)-R95</f>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="B96" s="4" t="n">
-        <v>1</v>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 290</t>
+        </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="4" t="n">
         <v>0</v>
@@ -6772,32 +7415,32 @@
         <v>0</v>
       </c>
       <c r="I96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J96" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L96" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="N96" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P96" s="4" t="n">
+      <c r="Q96" s="4" t="n">
         <v>498</v>
       </c>
-      <c r="Q96" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" s="4" t="n">
         <v>0</v>
       </c>
@@ -6811,28 +7454,34 @@
         <v>0</v>
       </c>
       <c r="V96" s="4" t="n">
-        <v>1008</v>
+        <v>0</v>
+      </c>
+      <c r="W96" s="4">
+        <f>SUM(C96:Q96)-R96</f>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
         <v>291</v>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>1</v>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 291</t>
+        </is>
       </c>
       <c r="C97" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D97" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="n">
         <v>922</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G97" s="4" t="n">
         <v>0</v>
       </c>
@@ -6879,15 +7528,21 @@
         <v>0</v>
       </c>
       <c r="V97" s="4" t="n">
-        <v>925</v>
+        <v>0</v>
+      </c>
+      <c r="W97" s="4">
+        <f>SUM(C97:Q97)-R97</f>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
         <v>292</v>
       </c>
-      <c r="B98" s="4" t="n">
-        <v>0</v>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 292</t>
+        </is>
       </c>
       <c r="C98" s="4" t="n">
         <v>0</v>
@@ -6896,11 +7551,11 @@
         <v>0</v>
       </c>
       <c r="E98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G98" s="4" t="n">
         <v>0</v>
       </c>
@@ -6947,15 +7602,21 @@
         <v>0</v>
       </c>
       <c r="V98" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="W98" s="4">
+        <f>SUM(C98:Q98)-R98</f>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
         <v>293</v>
       </c>
-      <c r="B99" s="4" t="n">
-        <v>0</v>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 293</t>
+        </is>
       </c>
       <c r="C99" s="4" t="n">
         <v>0</v>
@@ -6964,11 +7625,11 @@
         <v>0</v>
       </c>
       <c r="E99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F99" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G99" s="4" t="n">
         <v>0</v>
       </c>
@@ -7015,30 +7676,36 @@
         <v>0</v>
       </c>
       <c r="V99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="W99" s="4">
+        <f>SUM(C99:Q99)-R99</f>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
         <v>294</v>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 294</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
         <v>682</v>
       </c>
-      <c r="C100" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="n">
         <v>8</v>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>0</v>
@@ -7083,22 +7750,28 @@
         <v>0</v>
       </c>
       <c r="V100" s="4" t="n">
-        <v>694</v>
+        <v>0</v>
+      </c>
+      <c r="W100" s="4">
+        <f>SUM(C100:Q100)-R100</f>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
         <v>295</v>
       </c>
-      <c r="B101" s="4" t="n">
-        <v>0</v>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 295</t>
+        </is>
       </c>
       <c r="C101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D101" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E101" s="4" t="n">
         <v>0</v>
       </c>
@@ -7151,15 +7824,21 @@
         <v>0</v>
       </c>
       <c r="V101" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="W101" s="4">
+        <f>SUM(C101:Q101)-R101</f>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
         <v>296</v>
       </c>
-      <c r="B102" s="4" t="n">
-        <v>0</v>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 296</t>
+        </is>
       </c>
       <c r="C102" s="4" t="n">
         <v>0</v>
@@ -7174,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" s="4" t="n">
         <v>1</v>
@@ -7183,29 +7862,29 @@
         <v>1</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="4" t="n">
         <v>823</v>
       </c>
-      <c r="N102" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P102" s="4" t="n">
+      <c r="Q102" s="4" t="n">
         <v>827</v>
       </c>
-      <c r="Q102" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" s="4" t="n">
         <v>0</v>
       </c>
@@ -7219,30 +7898,36 @@
         <v>0</v>
       </c>
       <c r="V102" s="4" t="n">
-        <v>1658</v>
+        <v>0</v>
+      </c>
+      <c r="W102" s="4">
+        <f>SUM(C102:Q102)-R102</f>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
         <v>297</v>
       </c>
-      <c r="B103" s="4" t="n">
-        <v>0</v>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 297</t>
+        </is>
       </c>
       <c r="C103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D103" s="4" t="n">
+      <c r="E103" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="F103" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G103" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="4" t="n">
         <v>0</v>
@@ -7287,28 +7972,34 @@
         <v>0</v>
       </c>
       <c r="V103" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="W103" s="4">
+        <f>SUM(C103:Q103)-R103</f>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
         <v>298</v>
       </c>
-      <c r="B104" s="4" t="n">
-        <v>0</v>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 298</t>
+        </is>
       </c>
       <c r="C104" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="E104" s="4" t="n">
+      <c r="F104" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="F104" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G104" s="4" t="n">
         <v>0</v>
       </c>
@@ -7355,31 +8046,37 @@
         <v>0</v>
       </c>
       <c r="V104" s="4" t="n">
-        <v>129</v>
+        <v>0</v>
+      </c>
+      <c r="W104" s="4">
+        <f>SUM(C104:Q104)-R104</f>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
         <v>299</v>
       </c>
-      <c r="B105" s="4" t="n">
-        <v>0</v>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 299</t>
+        </is>
       </c>
       <c r="C105" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="G105" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H105" s="4" t="n">
         <v>0</v>
       </c>
@@ -7423,30 +8120,36 @@
         <v>0</v>
       </c>
       <c r="V105" s="4" t="n">
-        <v>93</v>
+        <v>0</v>
+      </c>
+      <c r="W105" s="4">
+        <f>SUM(C105:Q105)-R105</f>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 300</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C106" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="E106" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F106" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="4" t="n">
         <v>0</v>
@@ -7491,28 +8194,34 @@
         <v>0</v>
       </c>
       <c r="V106" s="4" t="n">
-        <v>74</v>
+        <v>0</v>
+      </c>
+      <c r="W106" s="4">
+        <f>SUM(C106:Q106)-R106</f>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
         <v>301</v>
       </c>
-      <c r="B107" s="4" t="n">
-        <v>0</v>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 301</t>
+        </is>
       </c>
       <c r="C107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="D107" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
         <v>912</v>
       </c>
-      <c r="F107" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G107" s="4" t="n">
         <v>0</v>
       </c>
@@ -7559,30 +8268,36 @@
         <v>0</v>
       </c>
       <c r="V107" s="4" t="n">
-        <v>938</v>
+        <v>0</v>
+      </c>
+      <c r="W107" s="4">
+        <f>SUM(C107:Q107)-R107</f>
+        <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
         <v>302</v>
       </c>
-      <c r="B108" s="4" t="n">
-        <v>0</v>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 302</t>
+        </is>
       </c>
       <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D108" s="4" t="n">
+      <c r="E108" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E108" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F108" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="4" t="n">
         <v>0</v>
@@ -7627,46 +8342,52 @@
         <v>0</v>
       </c>
       <c r="V108" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="W108" s="4">
+        <f>SUM(C108:Q108)-R108</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
         <v>303</v>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 303</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C109" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D109" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E109" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="J109" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L109" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M109" s="4" t="n">
         <v>0</v>
       </c>
@@ -7695,31 +8416,37 @@
         <v>0</v>
       </c>
       <c r="V109" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
+      </c>
+      <c r="W109" s="4">
+        <f>SUM(C109:Q109)-R109</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
         <v>304</v>
       </c>
-      <c r="B110" s="4" t="n">
-        <v>0</v>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 304</t>
+        </is>
       </c>
       <c r="C110" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E110" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G110" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H110" s="4" t="n">
         <v>0</v>
       </c>
@@ -7763,30 +8490,36 @@
         <v>0</v>
       </c>
       <c r="V110" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="W110" s="4">
+        <f>SUM(C110:Q110)-R110</f>
+        <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
         <v>305</v>
       </c>
-      <c r="B111" s="4" t="n">
-        <v>0</v>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 305</t>
+        </is>
       </c>
       <c r="C111" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E111" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F111" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="4" t="n">
         <v>0</v>
@@ -7831,31 +8564,37 @@
         <v>0</v>
       </c>
       <c r="V111" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="W111" s="4">
+        <f>SUM(C111:Q111)-R111</f>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
         <v>306</v>
       </c>
-      <c r="B112" s="4" t="n">
-        <v>0</v>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 306</t>
+        </is>
       </c>
       <c r="C112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D112" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="G112" s="4" t="n">
         <v>602</v>
       </c>
-      <c r="G112" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H112" s="4" t="n">
         <v>0</v>
       </c>
@@ -7899,31 +8638,37 @@
         <v>0</v>
       </c>
       <c r="V112" s="4" t="n">
-        <v>662</v>
+        <v>0</v>
+      </c>
+      <c r="W112" s="4">
+        <f>SUM(C112:Q112)-R112</f>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
         <v>307</v>
       </c>
-      <c r="B113" s="4" t="n">
-        <v>0</v>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 307</t>
+        </is>
       </c>
       <c r="C113" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E113" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="4" t="n">
         <v>802</v>
       </c>
-      <c r="G113" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H113" s="4" t="n">
         <v>0</v>
       </c>
@@ -7967,31 +8712,37 @@
         <v>0</v>
       </c>
       <c r="V113" s="4" t="n">
-        <v>809</v>
+        <v>0</v>
+      </c>
+      <c r="W113" s="4">
+        <f>SUM(C113:Q113)-R113</f>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
         <v>308</v>
       </c>
-      <c r="B114" s="4" t="n">
-        <v>0</v>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 308</t>
+        </is>
       </c>
       <c r="C114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D114" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="n">
         <v>602</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="G114" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G114" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H114" s="4" t="n">
         <v>0</v>
       </c>
@@ -8035,40 +8786,46 @@
         <v>0</v>
       </c>
       <c r="V114" s="4" t="n">
-        <v>628</v>
+        <v>0</v>
+      </c>
+      <c r="W114" s="4">
+        <f>SUM(C114:Q114)-R114</f>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
         <v>309</v>
       </c>
-      <c r="B115" s="4" t="n">
-        <v>0</v>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 309</t>
+        </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D115" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E115" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="G115" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G115" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H115" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J115" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K115" s="4" t="n">
         <v>0</v>
       </c>
@@ -8085,11 +8842,11 @@
         <v>0</v>
       </c>
       <c r="P115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="4" t="n">
         <v>870</v>
       </c>
-      <c r="Q115" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" s="4" t="n">
         <v>0</v>
       </c>
@@ -8103,15 +8860,21 @@
         <v>0</v>
       </c>
       <c r="V115" s="4" t="n">
-        <v>885</v>
+        <v>0</v>
+      </c>
+      <c r="W115" s="4">
+        <f>SUM(C115:Q115)-R115</f>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
         <v>310</v>
       </c>
-      <c r="B116" s="4" t="n">
-        <v>0</v>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 310</t>
+        </is>
       </c>
       <c r="C116" s="4" t="n">
         <v>0</v>
@@ -8172,27 +8935,33 @@
       </c>
       <c r="V116" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="W116" s="4">
+        <f>SUM(C116:Q116)-R116</f>
+        <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
         <v>311</v>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 311</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="C117" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="F117" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="F117" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G117" s="4" t="n">
         <v>0</v>
       </c>
@@ -8239,15 +9008,21 @@
         <v>0</v>
       </c>
       <c r="V117" s="4" t="n">
-        <v>245</v>
+        <v>0</v>
+      </c>
+      <c r="W117" s="4">
+        <f>SUM(C117:Q117)-R117</f>
+        <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
         <v>312</v>
       </c>
-      <c r="B118" s="4" t="n">
-        <v>0</v>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 312</t>
+        </is>
       </c>
       <c r="C118" s="4" t="n">
         <v>0</v>
@@ -8259,11 +9034,11 @@
         <v>0</v>
       </c>
       <c r="F118" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G118" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H118" s="4" t="n">
         <v>0</v>
       </c>
@@ -8307,15 +9082,21 @@
         <v>0</v>
       </c>
       <c r="V118" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="W118" s="4">
+        <f>SUM(C118:Q118)-R118</f>
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
         <v>313</v>
       </c>
-      <c r="B119" s="4" t="n">
-        <v>0</v>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 313</t>
+        </is>
       </c>
       <c r="C119" s="4" t="n">
         <v>0</v>
@@ -8324,23 +9105,23 @@
         <v>0</v>
       </c>
       <c r="E119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F119" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H119" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J119" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K119" s="4" t="n">
         <v>0</v>
       </c>
@@ -8348,20 +9129,20 @@
         <v>0</v>
       </c>
       <c r="M119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="4" t="n">
         <v>613</v>
       </c>
-      <c r="N119" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O119" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="4" t="n">
         <v>616</v>
       </c>
-      <c r="Q119" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" s="4" t="n">
         <v>0</v>
       </c>
@@ -8375,15 +9156,21 @@
         <v>0</v>
       </c>
       <c r="V119" s="4" t="n">
-        <v>1237</v>
+        <v>0</v>
+      </c>
+      <c r="W119" s="4">
+        <f>SUM(C119:Q119)-R119</f>
+        <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
         <v>324</v>
       </c>
-      <c r="B120" s="4" t="n">
-        <v>0</v>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 324</t>
+        </is>
       </c>
       <c r="C120" s="4" t="n">
         <v>0</v>
@@ -8401,35 +9188,35 @@
         <v>0</v>
       </c>
       <c r="H120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I120" s="4" t="n">
+      <c r="J120" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J120" s="4" t="n">
+      <c r="K120" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K120" s="4" t="n">
+      <c r="L120" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="L120" s="4" t="n">
+      <c r="M120" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M120" s="4" t="n">
+      <c r="N120" s="4" t="n">
         <v>598</v>
       </c>
-      <c r="N120" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P120" s="4" t="n">
+      <c r="Q120" s="4" t="n">
         <v>601</v>
       </c>
-      <c r="Q120" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" s="4" t="n">
         <v>0</v>
       </c>
@@ -8443,61 +9230,67 @@
         <v>0</v>
       </c>
       <c r="V120" s="4" t="n">
-        <v>1222</v>
+        <v>0</v>
+      </c>
+      <c r="W120" s="4">
+        <f>SUM(C120:Q120)-R120</f>
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
         <v>327</v>
       </c>
-      <c r="B121" s="4" t="n">
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 327</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C121" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D121" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J121" s="4" t="n">
+      <c r="K121" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K121" s="4" t="n">
+      <c r="L121" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L121" s="4" t="n">
+      <c r="M121" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M121" s="4" t="n">
+      <c r="N121" s="4" t="n">
         <v>709</v>
       </c>
-      <c r="N121" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="P121" s="4" t="n">
+      <c r="Q121" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="Q121" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" s="4" t="n">
         <v>0</v>
       </c>
@@ -8511,61 +9304,67 @@
         <v>0</v>
       </c>
       <c r="V121" s="4" t="n">
-        <v>764</v>
+        <v>0</v>
+      </c>
+      <c r="W121" s="4">
+        <f>SUM(C121:Q121)-R121</f>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
         <v>351</v>
       </c>
-      <c r="B122" s="4" t="n">
-        <v>0</v>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 351</t>
+        </is>
       </c>
       <c r="C122" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E122" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F122" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" s="4" t="n">
         <v>773</v>
       </c>
-      <c r="N122" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P122" s="4" t="n">
+      <c r="Q122" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="Q122" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" s="4" t="n">
         <v>0</v>
       </c>
@@ -8579,61 +9378,67 @@
         <v>0</v>
       </c>
       <c r="V122" s="4" t="n">
-        <v>962</v>
+        <v>0</v>
+      </c>
+      <c r="W122" s="4">
+        <f>SUM(C122:Q122)-R122</f>
+        <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
         <v>355</v>
       </c>
-      <c r="B123" s="4" t="n">
-        <v>0</v>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 355</t>
+        </is>
       </c>
       <c r="C123" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H123" s="4" t="n">
+      <c r="I123" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I123" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K123" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="L123" s="4" t="n">
         <v>10</v>
       </c>
       <c r="M123" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N123" s="4" t="n">
         <v>764</v>
       </c>
-      <c r="N123" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O123" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="4" t="n">
         <v>774</v>
       </c>
-      <c r="Q123" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" s="4" t="n">
         <v>0</v>
       </c>
@@ -8647,25 +9452,31 @@
         <v>0</v>
       </c>
       <c r="V123" s="4" t="n">
-        <v>1569</v>
+        <v>0</v>
+      </c>
+      <c r="W123" s="4">
+        <f>SUM(C123:Q123)-R123</f>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
         <v>366</v>
       </c>
-      <c r="B124" s="4" t="n">
-        <v>0</v>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 366</t>
+        </is>
       </c>
       <c r="C124" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E124" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F124" s="4" t="n">
         <v>0</v>
       </c>
@@ -8700,11 +9511,11 @@
         <v>0</v>
       </c>
       <c r="Q124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="R124" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" s="4" t="n">
         <v>0</v>
       </c>
@@ -8715,18 +9526,24 @@
         <v>0</v>
       </c>
       <c r="V124" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
+      </c>
+      <c r="W124" s="4">
+        <f>SUM(C124:Q124)-R124</f>
+        <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
         <v>368</v>
       </c>
-      <c r="B125" s="4" t="n">
-        <v>0</v>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 368</t>
+        </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="4" t="n">
         <v>1</v>
@@ -8735,41 +9552,41 @@
         <v>1</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J125" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="K125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L125" s="4" t="n">
+      <c r="M125" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M125" s="4" t="n">
+      <c r="N125" s="4" t="n">
         <v>641</v>
       </c>
-      <c r="N125" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O125" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q125" s="4" t="n">
         <v>642</v>
       </c>
-      <c r="Q125" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" s="4" t="n">
         <v>0</v>
       </c>
@@ -8783,15 +9600,21 @@
         <v>0</v>
       </c>
       <c r="V125" s="4" t="n">
-        <v>1300</v>
+        <v>0</v>
+      </c>
+      <c r="W125" s="4">
+        <f>SUM(C125:Q125)-R125</f>
+        <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
         <v>372</v>
       </c>
-      <c r="B126" s="4" t="n">
-        <v>4</v>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 372</t>
+        </is>
       </c>
       <c r="C126" s="4" t="n">
         <v>4</v>
@@ -8800,7 +9623,7 @@
         <v>4</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F126" s="4" t="n">
         <v>0</v>
@@ -8809,11 +9632,11 @@
         <v>0</v>
       </c>
       <c r="H126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I126" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J126" s="4" t="n">
         <v>0</v>
       </c>
@@ -8851,61 +9674,67 @@
         <v>0</v>
       </c>
       <c r="V126" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="W126" s="4">
+        <f>SUM(C126:Q126)-R126</f>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
         <v>396</v>
       </c>
-      <c r="B127" s="4" t="n">
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 396</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C127" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D127" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="H127" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H127" s="4" t="n">
+      <c r="I127" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I127" s="4" t="n">
+      <c r="J127" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J127" s="4" t="n">
+      <c r="K127" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="K127" s="4" t="n">
+      <c r="L127" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L127" s="4" t="n">
+      <c r="M127" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M127" s="4" t="n">
+      <c r="N127" s="4" t="n">
         <v>819</v>
       </c>
-      <c r="N127" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O127" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="4" t="n">
         <v>828</v>
       </c>
-      <c r="Q127" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" s="4" t="n">
         <v>0</v>
       </c>
@@ -8919,27 +9748,33 @@
         <v>0</v>
       </c>
       <c r="V127" s="4" t="n">
-        <v>1679</v>
+        <v>0</v>
+      </c>
+      <c r="W127" s="4">
+        <f>SUM(C127:Q127)-R127</f>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
         <v>397</v>
       </c>
-      <c r="B128" s="4" t="n">
-        <v>0</v>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 397</t>
+        </is>
       </c>
       <c r="C128" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
         <v>0</v>
@@ -8951,29 +9786,29 @@
         <v>0</v>
       </c>
       <c r="J128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K128" s="4" t="n">
+      <c r="L128" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L128" s="4" t="n">
+      <c r="M128" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="M128" s="4" t="n">
+      <c r="N128" s="4" t="n">
         <v>460</v>
       </c>
-      <c r="N128" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O128" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="4" t="n">
         <v>462</v>
       </c>
-      <c r="Q128" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" s="4" t="n">
         <v>0</v>
       </c>
@@ -8987,40 +9822,46 @@
         <v>0</v>
       </c>
       <c r="V128" s="4" t="n">
-        <v>936</v>
+        <v>0</v>
+      </c>
+      <c r="W128" s="4">
+        <f>SUM(C128:Q128)-R128</f>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 398</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C129" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D129" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F129" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H129" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="J129" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K129" s="4" t="n">
         <v>0</v>
       </c>
@@ -9037,11 +9878,11 @@
         <v>0</v>
       </c>
       <c r="P129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Q129" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" s="4" t="n">
         <v>0</v>
       </c>
@@ -9055,34 +9896,40 @@
         <v>0</v>
       </c>
       <c r="V129" s="4" t="n">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="W129" s="4">
+        <f>SUM(C129:Q129)-R129</f>
+        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
         <v>403</v>
       </c>
-      <c r="B130" s="4" t="n">
-        <v>0</v>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 403</t>
+        </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E130" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="F130" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H130" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I130" s="4" t="n">
         <v>0</v>
       </c>
@@ -9090,26 +9937,26 @@
         <v>0</v>
       </c>
       <c r="K130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="L130" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="4" t="n">
         <v>425</v>
       </c>
-      <c r="N130" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O130" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="4" t="n">
         <v>431</v>
       </c>
-      <c r="Q130" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" s="4" t="n">
         <v>0</v>
       </c>
@@ -9123,15 +9970,21 @@
         <v>0</v>
       </c>
       <c r="V130" s="4" t="n">
-        <v>884</v>
+        <v>0</v>
+      </c>
+      <c r="W130" s="4">
+        <f>SUM(C130:Q130)-R130</f>
+        <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
         <v>418</v>
       </c>
-      <c r="B131" s="4" t="n">
-        <v>0</v>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 418</t>
+        </is>
       </c>
       <c r="C131" s="4" t="n">
         <v>0</v>
@@ -9192,60 +10045,66 @@
       </c>
       <c r="V131" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="W131" s="4">
+        <f>SUM(C131:Q131)-R131</f>
+        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
         <v>430</v>
       </c>
-      <c r="B132" s="4" t="n">
-        <v>0</v>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 430</t>
+        </is>
       </c>
       <c r="C132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D132" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E132" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H132" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="I132" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J132" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L132" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="4" t="n">
         <v>882</v>
       </c>
-      <c r="N132" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O132" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="4" t="n">
         <v>891</v>
       </c>
-      <c r="Q132" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" s="4" t="n">
         <v>0</v>
       </c>
@@ -9259,21 +10118,27 @@
         <v>0</v>
       </c>
       <c r="V132" s="4" t="n">
-        <v>1789</v>
+        <v>0</v>
+      </c>
+      <c r="W132" s="4">
+        <f>SUM(C132:Q132)-R132</f>
+        <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
         <v>459</v>
       </c>
-      <c r="B133" s="4" t="n">
-        <v>0</v>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 459</t>
+        </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" s="4" t="n">
         <v>0</v>
@@ -9300,20 +10165,20 @@
         <v>0</v>
       </c>
       <c r="M133" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="4" t="n">
         <v>722</v>
       </c>
-      <c r="N133" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O133" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="Q133" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" s="4" t="n">
         <v>0</v>
       </c>
@@ -9327,28 +10192,34 @@
         <v>0</v>
       </c>
       <c r="V133" s="4" t="n">
-        <v>801</v>
+        <v>0</v>
+      </c>
+      <c r="W133" s="4">
+        <f>SUM(C133:Q133)-R133</f>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
         <v>463</v>
       </c>
-      <c r="B134" s="4" t="n">
-        <v>3</v>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 463</t>
+        </is>
       </c>
       <c r="C134" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E134" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="F134" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="G134" s="4" t="n">
         <v>0</v>
       </c>
@@ -9380,11 +10251,11 @@
         <v>0</v>
       </c>
       <c r="Q134" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R134" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" s="4" t="n">
         <v>0</v>
       </c>
@@ -9395,40 +10266,46 @@
         <v>0</v>
       </c>
       <c r="V134" s="4" t="n">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="W134" s="4">
+        <f>SUM(C134:Q134)-R134</f>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
         <v>473</v>
       </c>
-      <c r="B135" s="4" t="n">
-        <v>0</v>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>Sircilla PS 473</t>
+        </is>
       </c>
       <c r="C135" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H135" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="I135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J135" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="K135" s="4" t="n">
         <v>0</v>
       </c>
@@ -9436,20 +10313,20 @@
         <v>0</v>
       </c>
       <c r="M135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="4" t="n">
         <v>630</v>
       </c>
-      <c r="N135" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O135" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="4" t="n">
         <v>622</v>
       </c>
-      <c r="Q135" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" s="4" t="n">
         <v>0</v>
       </c>
@@ -9463,93 +10340,265 @@
         <v>0</v>
       </c>
       <c r="V135" s="4" t="n">
-        <v>1282</v>
+        <v>0</v>
+      </c>
+      <c r="W135" s="4">
+        <f>SUM(C135:Q135)-R135</f>
+        <v/>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B136" s="6">
-        <f>SUM(B6:B135)</f>
-        <v/>
-      </c>
-      <c r="C136" s="6">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" s="8">
         <f>SUM(C6:C135)</f>
         <v/>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="8">
         <f>SUM(D6:D135)</f>
         <v/>
       </c>
-      <c r="E136" s="6">
+      <c r="E136" s="8">
         <f>SUM(E6:E135)</f>
         <v/>
       </c>
-      <c r="F136" s="6">
+      <c r="F136" s="8">
         <f>SUM(F6:F135)</f>
         <v/>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="8">
         <f>SUM(G6:G135)</f>
         <v/>
       </c>
-      <c r="H136" s="6">
+      <c r="H136" s="8">
         <f>SUM(H6:H135)</f>
         <v/>
       </c>
-      <c r="I136" s="6">
+      <c r="I136" s="8">
         <f>SUM(I6:I135)</f>
         <v/>
       </c>
-      <c r="J136" s="6">
+      <c r="J136" s="8">
         <f>SUM(J6:J135)</f>
         <v/>
       </c>
-      <c r="K136" s="6">
+      <c r="K136" s="8">
         <f>SUM(K6:K135)</f>
         <v/>
       </c>
-      <c r="L136" s="6">
+      <c r="L136" s="8">
         <f>SUM(L6:L135)</f>
         <v/>
       </c>
-      <c r="M136" s="6">
+      <c r="M136" s="8">
         <f>SUM(M6:M135)</f>
         <v/>
       </c>
-      <c r="N136" s="6">
+      <c r="N136" s="8">
         <f>SUM(N6:N135)</f>
         <v/>
       </c>
-      <c r="O136" s="6">
+      <c r="O136" s="8">
         <f>SUM(O6:O135)</f>
         <v/>
       </c>
-      <c r="P136" s="6">
+      <c r="P136" s="8">
         <f>SUM(P6:P135)</f>
         <v/>
       </c>
-      <c r="Q136" s="6">
+      <c r="Q136" s="8">
         <f>SUM(Q6:Q135)</f>
         <v/>
       </c>
-      <c r="R136" s="6">
+      <c r="R136" s="8">
         <f>SUM(R6:R135)</f>
         <v/>
       </c>
-      <c r="S136" s="6">
+      <c r="S136" s="8">
         <f>SUM(S6:S135)</f>
         <v/>
       </c>
-      <c r="T136" s="6">
+      <c r="T136" s="8">
         <f>SUM(T6:T135)</f>
         <v/>
       </c>
-      <c r="U136" s="6">
-        <f>SUM(U6:U135)</f>
+      <c r="U136" s="8">
+        <f>R136+S136</f>
+        <v/>
+      </c>
+      <c r="V136" s="8">
+        <f>SUM(V6:V135)</f>
+        <v/>
+      </c>
+      <c r="W136" s="8">
+        <f>SUM(C136:Q136)-R136</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" s="12">
+        <f>C136+C137</f>
+        <v/>
+      </c>
+      <c r="D138" s="12">
+        <f>D136+D137</f>
+        <v/>
+      </c>
+      <c r="E138" s="12">
+        <f>E136+E137</f>
+        <v/>
+      </c>
+      <c r="F138" s="12">
+        <f>F136+F137</f>
+        <v/>
+      </c>
+      <c r="G138" s="12">
+        <f>G136+G137</f>
+        <v/>
+      </c>
+      <c r="H138" s="12">
+        <f>H136+H137</f>
+        <v/>
+      </c>
+      <c r="I138" s="12">
+        <f>I136+I137</f>
+        <v/>
+      </c>
+      <c r="J138" s="12">
+        <f>J136+J137</f>
+        <v/>
+      </c>
+      <c r="K138" s="12">
+        <f>K136+K137</f>
+        <v/>
+      </c>
+      <c r="L138" s="12">
+        <f>L136+L137</f>
+        <v/>
+      </c>
+      <c r="M138" s="12">
+        <f>M136+M137</f>
+        <v/>
+      </c>
+      <c r="N138" s="12">
+        <f>N136+N137</f>
+        <v/>
+      </c>
+      <c r="O138" s="12">
+        <f>O136+O137</f>
+        <v/>
+      </c>
+      <c r="P138" s="12">
+        <f>P136+P137</f>
+        <v/>
+      </c>
+      <c r="Q138" s="12">
+        <f>Q136+Q137</f>
+        <v/>
+      </c>
+      <c r="R138" s="12">
+        <f>R136+R137</f>
+        <v/>
+      </c>
+      <c r="S138" s="12">
+        <f>S136+S137</f>
+        <v/>
+      </c>
+      <c r="T138" s="12">
+        <f>T136+T137</f>
+        <v/>
+      </c>
+      <c r="U138" s="12">
+        <f>U136+U137</f>
+        <v/>
+      </c>
+      <c r="V138" s="12">
+        <f>V136+V137</f>
+        <v/>
+      </c>
+      <c r="W138" s="12">
+        <f>SUM(C138:Q138)-R138</f>
         <v/>
       </c>
     </row>
